--- a/output/pdf_financials_xlsx/OGC.xlsx
+++ b/output/pdf_financials_xlsx/OGC.xlsx
@@ -1029,10 +1029,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.9360000000000001</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.002</v>
       </c>
       <c r="D12" s="1" t="inlineStr">
         <is>
@@ -1050,34 +1050,34 @@
         </is>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.000624</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="13">
@@ -2047,10 +2047,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>0.623</v>
+        <v>-0.313</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>0.075</v>
+        <v>0.073</v>
       </c>
       <c r="D27" s="1" t="inlineStr">
         <is>
@@ -2183,10 +2183,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>0.623</v>
+        <v>-0.313</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>0.075</v>
+        <v>0.073</v>
       </c>
       <c r="D29" s="1" t="inlineStr">
         <is>
@@ -48176,7 +48176,7 @@
       </c>
       <c r="D445" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E445" t="inlineStr">
@@ -52420,7 +52420,7 @@
       </c>
       <c r="D493" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E493" t="inlineStr">
@@ -57987,7 +57987,7 @@
       </c>
       <c r="D556" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E556" s="5" t="n">

--- a/output/pdf_financials_xlsx/OGC.xlsx
+++ b/output/pdf_financials_xlsx/OGC.xlsx
@@ -7782,10 +7782,10 @@
         <v>0</v>
       </c>
       <c r="O126" s="3" t="n">
-        <v>0</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="P126" s="3" t="n">
-        <v>0</v>
+        <v>-19.4</v>
       </c>
     </row>
     <row r="127">
@@ -35999,7 +35999,11 @@
           <t>Dividends paid to non-controlling interests 13</t>
         </is>
       </c>
-      <c r="D306" t="inlineStr"/>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>CashDividendsPaid</t>
+        </is>
+      </c>
       <c r="E306" t="inlineStr">
         <is>
           <t>-</t>
@@ -38119,7 +38123,11 @@
           <t>Dividends paid to non-controlling interests 14</t>
         </is>
       </c>
-      <c r="D330" t="inlineStr"/>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>CashDividendsPaid</t>
+        </is>
+      </c>
       <c r="E330" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/OGC.xlsx
+++ b/output/pdf_financials_xlsx/OGC.xlsx
@@ -1339,10 +1339,10 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>-0</v>
+        <v>0.112</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.021</v>
       </c>
       <c r="D17" s="1" t="inlineStr">
         <is>
@@ -1560,15 +1560,11 @@
           <t xml:space="preserve">    Net Income (Continuing Operations)</t>
         </is>
       </c>
-      <c r="B20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B20" s="3" t="n">
+        <v>0.735</v>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>0.054</v>
       </c>
       <c r="D20" s="1" t="inlineStr">
         <is>
@@ -1759,10 +1755,10 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>0.623</v>
+        <v>0.735</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>0.075</v>
+        <v>0.054</v>
       </c>
       <c r="D23" s="1" t="inlineStr">
         <is>
@@ -2343,10 +2339,10 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>17.97752808988764</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="D31" s="1" t="inlineStr">
         <is>
@@ -2694,10 +2690,8 @@
       <c r="F37" s="3" t="n">
         <v>2.7e-05</v>
       </c>
-      <c r="G37" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G37" s="3" t="n">
+        <v>0.023737</v>
       </c>
       <c r="H37" s="3" t="n">
         <v>42.3</v>
@@ -2862,37 +2856,35 @@
       <c r="F40" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G40" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G40" s="3" t="n">
+        <v>0.075919</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>0</v>
+        <v>81.7</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>0</v>
+        <v>90.7</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>0</v>
+        <v>88.5</v>
       </c>
       <c r="K40" s="3" t="n">
-        <v>0</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="L40" s="3" t="n">
-        <v>0</v>
+        <v>88.5</v>
       </c>
       <c r="M40" s="3" t="n">
-        <v>0</v>
+        <v>107</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>0</v>
+        <v>55.8</v>
       </c>
       <c r="O40" s="3" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P40" s="3" t="n">
-        <v>0</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="41">
@@ -2924,31 +2916,31 @@
         </is>
       </c>
       <c r="H41" s="3" t="n">
-        <v>42.3</v>
+        <v>124</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>21</v>
+        <v>111.7</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>6.9</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>7.5</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>24.1</v>
+        <v>112.6</v>
       </c>
       <c r="M41" s="3" t="n">
-        <v>34.1</v>
+        <v>141.1</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>44.2</v>
+        <v>100</v>
       </c>
       <c r="O41" s="3" t="n">
-        <v>13.7</v>
+        <v>16.8</v>
       </c>
       <c r="P41" s="3" t="n">
-        <v>17.4</v>
+        <v>25.3</v>
       </c>
     </row>
     <row r="42">
@@ -3316,31 +3308,31 @@
         </is>
       </c>
       <c r="H48" s="3" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>14.9</v>
+        <v>0</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>12.4</v>
+        <v>0</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>24.5</v>
+        <v>0</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>18.6</v>
+        <v>15.5</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>19.8</v>
+        <v>11.9</v>
       </c>
     </row>
     <row r="49">
@@ -4592,13 +4584,13 @@
         <v>0</v>
       </c>
       <c r="N70" s="3" t="n">
-        <v>0</v>
+        <v>33.2</v>
       </c>
       <c r="O70" s="3" t="n">
-        <v>0</v>
+        <v>28.1</v>
       </c>
       <c r="P70" s="3" t="n">
-        <v>0</v>
+        <v>19.9</v>
       </c>
     </row>
     <row r="71">
@@ -4648,13 +4640,13 @@
         <v>0</v>
       </c>
       <c r="N71" s="3" t="n">
-        <v>0</v>
+        <v>33.2</v>
       </c>
       <c r="O71" s="3" t="n">
-        <v>0</v>
+        <v>28.1</v>
       </c>
       <c r="P71" s="3" t="n">
-        <v>0</v>
+        <v>19.9</v>
       </c>
     </row>
     <row r="72">
@@ -4872,13 +4864,13 @@
         <v>54.9</v>
       </c>
       <c r="N75" s="3" t="n">
-        <v>98.7</v>
+        <v>65.5</v>
       </c>
       <c r="O75" s="3" t="n">
-        <v>109.2</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="P75" s="3" t="n">
-        <v>202.9</v>
+        <v>183</v>
       </c>
     </row>
     <row r="76">
@@ -5172,13 +5164,13 @@
         </is>
       </c>
       <c r="N80" s="3" t="n">
-        <v>0.03485084530609889</v>
+        <v>0.05400727020945127</v>
       </c>
       <c r="O80" s="3" t="n">
-        <v>0.02174928627043862</v>
+        <v>0.03633532312483779</v>
       </c>
       <c r="P80" s="3" t="n">
-        <v>0.0127361673414305</v>
+        <v>0.02112854251012146</v>
       </c>
     </row>
     <row r="81">
@@ -6155,10 +6147,10 @@
         </is>
       </c>
       <c r="B99" s="3" t="n">
-        <v>0.623</v>
+        <v>0.735</v>
       </c>
       <c r="C99" s="3" t="n">
-        <v>0.075</v>
+        <v>0.054</v>
       </c>
       <c r="D99" s="1" t="inlineStr">
         <is>
@@ -6272,16 +6264,16 @@
         <v>0</v>
       </c>
       <c r="M100" s="3" t="n">
-        <v>0</v>
+        <v>201.2</v>
       </c>
       <c r="N100" s="3" t="n">
-        <v>0</v>
+        <v>228.8</v>
       </c>
       <c r="O100" s="3" t="n">
-        <v>0</v>
+        <v>321.2</v>
       </c>
       <c r="P100" s="3" t="n">
-        <v>0</v>
+        <v>252</v>
       </c>
     </row>
     <row r="101">
@@ -6717,7 +6709,7 @@
         <v>0</v>
       </c>
       <c r="H108" s="3" t="n">
-        <v>0</v>
+        <v>17.7</v>
       </c>
       <c r="I108" s="3" t="n">
         <v>0</v>
@@ -7135,7 +7127,7 @@
         <v>0</v>
       </c>
       <c r="L115" s="3" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="M115" s="3" t="n">
         <v>0</v>
@@ -9731,7 +9723,11 @@
           <t>Lease liabilities 9</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>-</t>
@@ -34136,7 +34132,11 @@
           <t>Depreciation and amortization expense</t>
         </is>
       </c>
-      <c r="D285" t="inlineStr"/>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E285" t="inlineStr">
         <is>
           <t>-</t>
@@ -34759,7 +34759,11 @@
           <t>Deferred tax expense 19</t>
         </is>
       </c>
-      <c r="D292" t="inlineStr"/>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E292" t="inlineStr">
         <is>
           <t>-</t>
@@ -40792,7 +40796,11 @@
           <t>Proceeds from sale of investments</t>
         </is>
       </c>
-      <c r="D361" t="inlineStr"/>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E361" t="inlineStr">
         <is>
           <t>-</t>
@@ -43000,7 +43008,11 @@
           <t>Impairment charge</t>
         </is>
       </c>
-      <c r="D387" t="inlineStr"/>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>AssetImpairmentCharge</t>
+        </is>
+      </c>
       <c r="E387" t="inlineStr">
         <is>
           <t>-</t>
@@ -58361,7 +58373,11 @@
           <t>Net earnings/(loss) 54 512</t>
         </is>
       </c>
-      <c r="D560" t="inlineStr"/>
+      <c r="D560" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E560" s="5" t="n">
         <v>0.735</v>
       </c>
@@ -58806,7 +58822,11 @@
           <t>Net earnings/(loss) 54 512</t>
         </is>
       </c>
-      <c r="D565" t="inlineStr"/>
+      <c r="D565" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E565" s="5" t="n">
         <v>0.735</v>
       </c>
